--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N58_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N58_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.99769897512195</v>
+        <v>2.112126083457318</v>
       </c>
       <c r="D2" t="n">
-        <v>13.25772888583601</v>
+        <v>2.154380943948352</v>
       </c>
       <c r="E2" t="n">
-        <v>5.22996113064449</v>
+        <v>0.8498686837297297</v>
       </c>
       <c r="F2" t="n">
-        <v>6.641187233893067</v>
+        <v>1.079192925507623</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.18083158464858</v>
+        <v>4.416885132505394</v>
       </c>
       <c r="D3" t="n">
-        <v>27.42142580843064</v>
+        <v>4.45598169386998</v>
       </c>
       <c r="E3" t="n">
-        <v>5.22996113064449</v>
+        <v>0.8498686837297297</v>
       </c>
       <c r="F3" t="n">
-        <v>6.641187233893067</v>
+        <v>1.079192925507623</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.72515789842139</v>
+        <v>3.367838158493476</v>
       </c>
       <c r="D4" t="n">
-        <v>28.76836773850016</v>
+        <v>4.674859757506276</v>
       </c>
       <c r="E4" t="n">
-        <v>5.22996113064449</v>
+        <v>0.8498686837297297</v>
       </c>
       <c r="F4" t="n">
-        <v>6.641187233893067</v>
+        <v>1.079192925507623</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.59227218944265</v>
+        <v>2.04624423078443</v>
       </c>
       <c r="D5" t="n">
-        <v>12.25802649371911</v>
+        <v>1.991929305229355</v>
       </c>
       <c r="E5" t="n">
-        <v>5.22996113064449</v>
+        <v>0.8498686837297297</v>
       </c>
       <c r="F5" t="n">
-        <v>6.641187233893067</v>
+        <v>1.079192925507623</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.48066215181325</v>
+        <v>2.353107599669653</v>
       </c>
       <c r="D6" t="n">
-        <v>23.8797398573799</v>
+        <v>3.880457726824234</v>
       </c>
       <c r="E6" t="n">
-        <v>5.22996113064449</v>
+        <v>0.8498686837297297</v>
       </c>
       <c r="F6" t="n">
-        <v>6.641187233893067</v>
+        <v>1.079192925507623</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>12.14148180058847</v>
+        <v>1.972990792595626</v>
       </c>
       <c r="D7" t="n">
-        <v>12.4527380753075</v>
+        <v>2.023569937237469</v>
       </c>
       <c r="E7" t="n">
-        <v>5.22996113064449</v>
+        <v>0.8498686837297297</v>
       </c>
       <c r="F7" t="n">
-        <v>6.641187233893067</v>
+        <v>1.079192925507623</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>19.95054668162578</v>
+        <v>3.24196383576419</v>
       </c>
       <c r="D8" t="n">
-        <v>19.76579623617841</v>
+        <v>3.211941888378993</v>
       </c>
       <c r="E8" t="n">
-        <v>5.22996113064449</v>
+        <v>0.8498686837297297</v>
       </c>
       <c r="F8" t="n">
-        <v>6.641187233893067</v>
+        <v>1.079192925507623</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
